--- a/results/job_matches_2026-04-27.xlsx
+++ b/results/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,15 +513,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0b3232c657b0b6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9588dfdbeb5d98ef</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AXIOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Spark, Scala, Dask, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,40 +601,145 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab406fdc25efa811</t>
+          <t>https://www.indeed.com/viewjob?jk=ad31ec519f2de337</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Java Solution Architect</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AXIOM</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, BigQuery, Spark, Scala, Dask, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab406fdc25efa811</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Compass Group USA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Charlotte, NC, US USA</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D9" t="n">
         <v>11.1</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
         </is>

--- a/results/job_matches_2026-04-27.xlsx
+++ b/results/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,15 +513,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0b3232c657b0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9588dfdbeb5d98ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AXIOM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>AWS, Azure, GCP, BigQuery, Spark, Scala, Dask, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,145 +601,40 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad31ec519f2de337</t>
+          <t>https://www.indeed.com/viewjob?jk=ab406fdc25efa811</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AXIOM</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, BigQuery, Spark, Scala, Dask, Snowflake, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab406fdc25efa811</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Compass Group USA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
         </is>

--- a/results/job_matches_2026-04-27.xlsx
+++ b/results/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Java Application Support Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.6</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
+          <t>https://www.indeed.com/viewjob?jk=9deace07d50ab229</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+          <t>Software engineering intern | Skillsync</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,15 +548,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AXIOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Spark, Scala, Dask, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab406fdc25efa811</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ff70697f7c7e8d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,15 +626,50 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Compass Group USA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
         </is>

--- a/results/job_matches_2026-04-27.xlsx
+++ b/results/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Java Application Support Analyst</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,77 +478,77 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9deace07d50ab229</t>
+          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
+          <t>https://www.indeed.com/viewjob?jk=a0719fad36e544cf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software engineering intern | Skillsync</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,77 +556,77 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ff70697f7c7e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,322 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Software engineering intern | Skillsync</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Compass Group USA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Charlotte, NC, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D11" t="n">
         <v>11.1</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Cloud Database Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Smithfield, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Cloud Database Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Merrimack, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Cloud Database Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AWS API Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-27.xlsx
+++ b/results/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>AI &amp; Data Solution Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75279cc7e23ce8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Java Application Support Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,81 +517,81 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0719fad36e544cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9deace07d50ab229</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
+          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
+          <t>https://www.indeed.com/viewjob?jk=a0719fad36e544cf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software engineering intern | Skillsync</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,29 +661,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Senior Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,46 +692,46 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Software engineering intern | Skillsync</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
+          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Data Engineers</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,112 +846,497 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb86d071d17aa3e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
+          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Technical Architect - Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>WinWire</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Newport Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4ff70697f7c7e8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Eurest</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Redmond, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Compass Group USA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Cloud Database Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Smithfield, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Cloud Database Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Merrimack, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Cloud Database Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>AWS API Engineer</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>AK, US USA</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D25" t="n">
         <v>10.4</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IT Business Analyst II</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NFI Industries</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b12be44615688132</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-27.xlsx
+++ b/results/job_matches_2026-04-27.xlsx
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Application Support Analyst</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,81 +517,81 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9deace07d50ab229</t>
+          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0719fad36e544cf</t>
+          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
+          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Software engineering intern | Skillsync</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,24 +661,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Hybrid)</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,29 +701,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Senior Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,112 +731,112 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
+          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software engineering intern | Skillsync</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
+          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineers</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>HAVI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,102 +846,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb86d071d17aa3e</t>
+          <t>https://www.indeed.com/viewjob?jk=6868b35e2b442275</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Technical Architect - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>WinWire</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
+          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
+          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Technical Architect - Data &amp; Analytics</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>HAVI Logistics GmbH</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+          <t>https://www.indeed.com/viewjob?jk=6afcd0c46d1aac2f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Polars, PostgreSQL, MongoDB, ETL, Power BI, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ff70697f7c7e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e146f6b8fe54d046</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
+          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
+          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-27.xlsx
+++ b/results/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI &amp; Data Solution Architect</t>
+          <t>Salesforce Financial Services Cloud Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Google Cloud Platform, GCP</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75279cc7e23ce8</t>
+          <t>https://www.indeed.com/viewjob?jk=452ad96763321f8b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Cloud IAM Engineer (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,15 +513,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>27.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
+          <t>https://www.indeed.com/viewjob?jk=4824fb9c6cc39b44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>AI &amp; Data Solution Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75279cc7e23ce8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Full Stack Golang Engineer (AWS | Python | React/Angular/Vue)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8c7a7f43e72aac</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>API Security IAM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
+          <t>https://www.indeed.com/viewjob?jk=0585ca531cf89a02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software engineering intern | Skillsync</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,207 +671,207 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2967a40f711a6e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Hybrid)</t>
+          <t>Data Lakehouse Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>SEACORP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Middletown, RI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Hadoop, Hive, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
+          <t>https://www.indeed.com/viewjob?jk=677bf2a9ae41af7d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IAM Compliance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8befff8bb32799</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
+          <t>https://www.indeed.com/viewjob?jk=a3cac0f27d3d0ec0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HAVI</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6868b35e2b442275</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Technical Architect - Data &amp; Analytics</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Software engineering intern | Skillsync</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HAVI Logistics GmbH</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6afcd0c46d1aac2f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Infrastructure Engineer</t>
+          <t>Senior Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Polars, PostgreSQL, MongoDB, ETL, Power BI, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e146f6b8fe54d046</t>
+          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Senior Business Intelligence Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Enova International</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>API Security IAM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,84 +1161,84 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd21204e38d8804</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
+          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Cloud Governance Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,15 +1248,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,40 +1301,1440 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
+          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>AWS API Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>E Source</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Consultant, AI &amp; Data Engineering</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Castleton Tower</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Java SDK / Library Developer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2084228c36d871bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Cloud Disaster Recovery Architect</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HI, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caa3dd413db07a1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HAVI</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6868b35e2b442275</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Technical Architect - Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>WinWire</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Newport Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Solutions Architect | AI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Trace3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Solutions Architect | AI</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Trace3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Solutions Architect | AI</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Trace3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Solutions Architect | AI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Trace3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Service Cloud Developer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Cloud Network Architect</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Cloud Migration Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Java SDK / Library Developer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7e739271640a7a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HAVI Logistics GmbH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6afcd0c46d1aac2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Data Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Polars, PostgreSQL, MongoDB, ETL, Power BI, Docker</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e146f6b8fe54d046</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Multi-Cloud Networking Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Eurest</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Redmond, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Compass Group USA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Google Cloud Platform, Vertex AI, MySQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49fb7f28e099bc48</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AWS API Gateway Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a35dc5b0dda48351</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Cloud Database Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Smithfield, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Cloud Database Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Merrimack, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Cloud Database Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AWS API Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AWS API Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AWS API Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Service Cloud Developer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>IDEXX Laboratories</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, SQS, ECS, RDS, Google Cloud Platform, Kafka, NoSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c57f26611e26283</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Cloud Network Architect</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c56248b7666452f</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Java QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bd189429512e52f</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Cloud Identity Architect</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03a07e922d166cc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>L&amp;T Technology Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Novi, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>IT Business Analyst II</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>NFI Industries</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Camden, NJ, US USA</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D66" t="n">
         <v>10.4</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b12be44615688132</t>
         </is>

--- a/results/job_matches_2026-04-27.xlsx
+++ b/results/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,95 +538,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI &amp; Data Solution Architect</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>25.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Google Cloud Platform, GCP</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75279cc7e23ce8</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7c40f9e99ad12f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Golang Engineer (AWS | Python | React/Angular/Vue)</t>
+          <t>AI &amp; Data Solution Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8c7a7f43e72aac</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75279cc7e23ce8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>API Security IAM</t>
+          <t>Full Stack Golang Engineer (AWS | Python | React/Angular/Vue)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0585ca531cf89a02</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8c7a7f43e72aac</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2967a40f711a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1b4cd21f275b79</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>API Security IAM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
+          <t>https://www.indeed.com/viewjob?jk=0585ca531cf89a02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Lakehouse Architect</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SEACORP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Middletown, RI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Hadoop, Hive, Spark, Scala, Kafka, MongoDB</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677bf2a9ae41af7d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2967a40f711a6e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IAM Compliance</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8befff8bb32799</t>
+          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>IAM Compliance</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3cac0f27d3d0ec0</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8befff8bb32799</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
+          <t>https://www.indeed.com/viewjob?jk=a3cac0f27d3d0ec0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Data Lakehouse Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>SEACORP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Middletown, RI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Hadoop, Hive, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
+          <t>https://www.indeed.com/viewjob?jk=677bf2a9ae41af7d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software engineering intern | Skillsync</t>
+          <t>DATA SOLUTION ARCHITECT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Care.org</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
+          <t>https://www.indeed.com/viewjob?jk=2846f65aa9294d0e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Hybrid)</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer (Hybrid)</t>
+          <t>Software engineering intern | Skillsync</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Enova International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,84 +1056,84 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
+          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>API Security IAM</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, Oracle, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,84 +1161,84 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd21204e38d8804</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Business Intelligence Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Enova International</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Governance Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,15 +1248,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
+          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Cloud Governance Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,102 +1301,102 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
+          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Consultant, AI &amp; Data Engineering</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Castleton Tower</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
+          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2084228c36d871bf</t>
+          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Architect</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa3dd413db07a1e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Consultant, AI &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HAVI</t>
+          <t>Castleton Tower</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6868b35e2b442275</t>
+          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Technical Architect - Data &amp; Analytics</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2084228c36d871bf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Senior Cloud Disaster Recovery Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+          <t>https://www.indeed.com/viewjob?jk=caa3dd413db07a1e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>HAVI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
+          <t>https://www.indeed.com/viewjob?jk=6868b35e2b442275</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Technical Architect - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>WinWire</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
+          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
+          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
+          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e739271640a7a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HAVI Logistics GmbH</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6afcd0c46d1aac2f</t>
+          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Infrastructure Engineer</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Polars, PostgreSQL, MongoDB, ETL, Power BI, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e146f6b8fe54d046</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
+          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,77 +2026,77 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2162,11 +2162,11 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Google Cloud Platform, Vertex AI, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fb7f28e099bc48</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e739271640a7a3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HAVI Logistics GmbH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35dc5b0dda48351</t>
+          <t>https://www.indeed.com/viewjob?jk=6afcd0c46d1aac2f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Polars, PostgreSQL, MongoDB, ETL, Power BI, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
+          <t>https://www.indeed.com/viewjob?jk=e146f6b8fe54d046</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
+          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,49 +2386,49 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,15 +2438,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a35dc5b0dda48351</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
+          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
         </is>
       </c>
     </row>
@@ -2512,11 +2512,11 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Google Cloud Platform, Vertex AI, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+          <t>https://www.indeed.com/viewjob?jk=49fb7f28e099bc48</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Google Cloud Platform, Kafka, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c57f26611e26283</t>
+          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c56248b7666452f</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Java QA Automation Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd189429512e52f</t>
+          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a07e922d166cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
+          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IT Business Analyst II</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,15 +2726,505 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AWS API Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>AWS API Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AWS API Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Data Engineer (remote)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Claritev</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Cloud Network Architect</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c56248b7666452f</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Java QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bd189429512e52f</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Cloud Identity Architect</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03a07e922d166cc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Cellular Sales, Verizon Authorized Retailer</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Impact.Com</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Impact.Com</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>IDEXX Laboratories</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, SQS, ECS, RDS, Google Cloud Platform, Kafka, NoSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c57f26611e26283</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>L&amp;T Technology Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Novi, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>IT Business Analyst II</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NFI Industries</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b12be44615688132</t>
         </is>

--- a/results/job_matches_2026-04-27.xlsx
+++ b/results/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>API Security IAM</t>
+          <t>Senior Software Engineer – Python</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Smart IS (SMC-Private) Limited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>PK USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0585ca531cf89a02</t>
+          <t>https://www.indeed.com/viewjob?jk=6466751badd1a073</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2967a40f711a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7fe60e6480b1a64</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>API Security IAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
+          <t>https://www.indeed.com/viewjob?jk=0585ca531cf89a02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IAM Compliance</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,15 +793,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, Scala</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8befff8bb32799</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2967a40f711a6e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3cac0f27d3d0ec0</t>
+          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Lakehouse Architect</t>
+          <t>IAM Compliance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SEACORP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Middletown, RI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Hadoop, Hive, Spark, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677bf2a9ae41af7d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8befff8bb32799</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
+          <t>https://www.indeed.com/viewjob?jk=a3cac0f27d3d0ec0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DATA SOLUTION ARCHITECT</t>
+          <t>Data Lakehouse Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Care.org</t>
+          <t>SEACORP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Middletown, RI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, S3, RDS, Hadoop, Hive, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2846f65aa9294d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=677bf2a9ae41af7d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>DATA SOLUTION ARCHITECT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Care.org</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2846f65aa9294d0e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software engineering intern | Skillsync</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
+          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Hybrid)</t>
+          <t>Software engineering intern | Skillsync</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,104 +1116,104 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer (Hybrid)</t>
+          <t>Senior Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Enova International</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
+          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Business Intelligence Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Enova International</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,94 +1266,94 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Governance Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
+          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Governance Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
+          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,77 +1396,77 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
+          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Consultant, AI &amp; Data Engineering</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Castleton Tower</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
+          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2084228c36d871bf</t>
+          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Architect</t>
+          <t>Senior Consultant, AI &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Castleton Tower</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa3dd413db07a1e</t>
+          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HAVI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6868b35e2b442275</t>
+          <t>https://www.indeed.com/viewjob?jk=2084228c36d871bf</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Technical Architect - Data &amp; Analytics</t>
+          <t>Senior Cloud Disaster Recovery Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=caa3dd413db07a1e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>HAVI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+          <t>https://www.indeed.com/viewjob?jk=6868b35e2b442275</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Technical Architect - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>WinWire</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
+          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
+          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
+          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
+          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
         </is>
       </c>
     </row>
@@ -2066,29 +2066,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
+          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
+          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,24 +2131,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e739271640a7a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HAVI Logistics GmbH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6afcd0c46d1aac2f</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Infrastructure Engineer</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Polars, PostgreSQL, MongoDB, ETL, Power BI, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e146f6b8fe54d046</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e739271640a7a3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HAVI Logistics GmbH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
+          <t>https://www.indeed.com/viewjob?jk=6afcd0c46d1aac2f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Polars, PostgreSQL, MongoDB, ETL, Power BI, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
+          <t>https://www.indeed.com/viewjob?jk=e146f6b8fe54d046</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
+          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35dc5b0dda48351</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
+          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Google Cloud Platform, Vertex AI, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fb7f28e099bc48</t>
+          <t>https://www.indeed.com/viewjob?jk=a35dc5b0dda48351</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Google Cloud Platform, Vertex AI, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
+          <t>https://www.indeed.com/viewjob?jk=49fb7f28e099bc48</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
+          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>MLOps Engineer - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
+          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
+          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c56248b7666452f</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Java QA Automation Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd189429512e52f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a07e922d166cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cellular Sales, Verizon Authorized Retailer</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
+          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,24 +3076,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
+          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Google Cloud Platform, Kafka, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c57f26611e26283</t>
+          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
+          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>IT Business Analyst II</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,15 +3216,400 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Cloud Network Architect</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c56248b7666452f</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Java QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bd189429512e52f</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Cloud Identity Architect</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03a07e922d166cc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Cellular Sales, Verizon Authorized Retailer</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Data Scientist III- Human Capital Data and Analytics Enablement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Snowflake, NoSQL, Tableau, Git, Python</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6941160617103aa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Impact.Com</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Impact.Com</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>IDEXX Laboratories</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, SQS, ECS, RDS, Google Cloud Platform, Kafka, NoSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c57f26611e26283</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>L&amp;T Technology Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Novi, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>IT Business Analyst II</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NFI Industries</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b12be44615688132</t>
         </is>

--- a/results/job_matches_2026-04-27.xlsx
+++ b/results/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Python</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Smart IS (SMC-Private) Limited</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PK USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6466751badd1a073</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2390ad9f6c9780</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>DATA SOLUTION ARCHITECT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Care.org</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
+          <t>https://www.indeed.com/viewjob?jk=2846f65aa9294d0e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DATA SOLUTION ARCHITECT</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Care.org</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2846f65aa9294d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
+          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Software engineering intern | Skillsync</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
+          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software engineering intern | Skillsync</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,24 +1116,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Senior Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1156,64 +1156,64 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Hybrid)</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Senior Business Intelligence Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Enova International</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
+          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer (Hybrid)</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Enova International</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,24 +1291,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
+          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Cloud Governance Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1318,15 +1318,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Cloud Governance Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
+          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
         </is>
       </c>
     </row>
@@ -1483,52 +1483,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
+          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Easterseals Southern California</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Consultant, AI &amp; Data Engineering</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Castleton Tower</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
+          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2084228c36d871bf</t>
+          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Architect</t>
+          <t>Senior Consultant, AI &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Castleton Tower</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa3dd413db07a1e</t>
+          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HAVI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6868b35e2b442275</t>
+          <t>https://www.indeed.com/viewjob?jk=2084228c36d871bf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Technical Architect - Data &amp; Analytics</t>
+          <t>Senior Cloud Disaster Recovery Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=caa3dd413db07a1e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>HAVI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+          <t>https://www.indeed.com/viewjob?jk=6868b35e2b442275</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Technical Architect - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>WinWire</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
+          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
+          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
+          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
+          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
+          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
+          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e739271640a7a3</t>
+          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HAVI Logistics GmbH</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6afcd0c46d1aac2f</t>
+          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Infrastructure Engineer</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Polars, PostgreSQL, MongoDB, ETL, Power BI, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e146f6b8fe54d046</t>
+          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e739271640a7a3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>HAVI Logistics GmbH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
+          <t>https://www.indeed.com/viewjob?jk=6afcd0c46d1aac2f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+          <t>Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,15 +2438,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Spark, Scala, Polars, PostgreSQL, MongoDB, ETL, Power BI, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e146f6b8fe54d046</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
+          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,15 +2508,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35dc5b0dda48351</t>
+          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
+          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Google Cloud Platform, Vertex AI, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fb7f28e099bc48</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
+          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
+          <t>https://www.indeed.com/viewjob?jk=a35dc5b0dda48351</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
+          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Machine Learning Platform</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Google Cloud Platform, Vertex AI, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
+          <t>https://www.indeed.com/viewjob?jk=49fb7f28e099bc48</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
+          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Florham Park, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Senior Digital Analytics Engineer - Customer Experience</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
+          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>MLOps Engineer - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
+          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
+          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
+          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
+          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c56248b7666452f</t>
+          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Java QA Automation Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,24 +3286,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd189429512e52f</t>
+          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a07e922d166cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cellular Sales, Verizon Authorized Retailer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
+          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Scientist III- Human Capital Data and Analytics Enablement</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Snowflake, NoSQL, Tableau, Git, Python</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6941160617103aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
+          <t>https://www.indeed.com/viewjob?jk=8c56248b7666452f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Java QA Automation Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd189429512e52f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Google Cloud Platform, Kafka, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c57f26611e26283</t>
+          <t>https://www.indeed.com/viewjob?jk=03a07e922d166cc3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Cellular Sales, Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
+          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IT Business Analyst II</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,15 +3601,225 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Data Scientist III- Human Capital Data and Analytics Enablement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Snowflake, NoSQL, Tableau, Git, Python</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6941160617103aa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Impact.Com</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>IDEXX Laboratories</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, SQS, ECS, RDS, Google Cloud Platform, Kafka, NoSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c57f26611e26283</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>L&amp;T Technology Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Novi, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>IT Business Analyst II</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NFI Industries</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b12be44615688132</t>
         </is>

--- a/results/job_matches_2026-04-27.xlsx
+++ b/results/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>API Security IAM</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0585ca531cf89a02</t>
+          <t>https://www.indeed.com/viewjob?jk=e96d0ff5e851a0dc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>API Security IAM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2967a40f711a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=0585ca531cf89a02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Lakehouse Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SEACORP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Manassas, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, S3, RDS, Hadoop, Hive, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
+          <t>https://www.indeed.com/viewjob?jk=677bf2a9ae41af7d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IAM Compliance</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, Scala</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8befff8bb32799</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2967a40f711a6e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3cac0f27d3d0ec0</t>
+          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Lakehouse Architect</t>
+          <t>IAM Compliance</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SEACORP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Middletown, RI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Hadoop, Hive, Spark, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677bf2a9ae41af7d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8befff8bb32799</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DATA SOLUTION ARCHITECT</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Care.org</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2846f65aa9294d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=a3cac0f27d3d0ec0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
+          <t>https://www.indeed.com/viewjob?jk=a0719fad36e544cf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>DATA SOLUTION ARCHITECT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Care.org</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2846f65aa9294d0e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software engineering intern | Skillsync</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Senior Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,29 +1121,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Hybrid)</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
+          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer (Hybrid)</t>
+          <t>Software engineering intern | Skillsync</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Enova International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
+          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Senior Business Intelligence Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Enova International</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
+          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,24 +1291,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud Governance Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1318,15 +1318,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
+          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
+          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
+          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Governance Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Easterseals Southern California</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
+          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,15 +1563,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
+          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Consultant, AI &amp; Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Castleton Tower</t>
+          <t>Easterseals Southern California</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
+          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2084228c36d871bf</t>
+          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Architect</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa3dd413db07a1e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Consultant, AI &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HAVI</t>
+          <t>Castleton Tower</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6868b35e2b442275</t>
+          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Technical Architect - Data &amp; Analytics</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2084228c36d871bf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Senior Cloud Disaster Recovery Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+          <t>https://www.indeed.com/viewjob?jk=caa3dd413db07a1e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>HAVI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=6868b35e2b442275</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Technical Architect - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>WinWire</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
+          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
+          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
+          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
+          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
+          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
+          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
+          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
+          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
+          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e739271640a7a3</t>
+          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HAVI Logistics GmbH</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6afcd0c46d1aac2f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Infrastructure Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Polars, PostgreSQL, MongoDB, ETL, Power BI, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e146f6b8fe54d046</t>
+          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
+          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
+          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Implementation Consultant - Solutions Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
+          <t>https://www.indeed.com/viewjob?jk=73dc903c92ca8eb2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,15 +2648,15 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35dc5b0dda48351</t>
+          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2722,11 +2722,11 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Google Cloud Platform, Vertex AI, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fb7f28e099bc48</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e739271640a7a3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>HAVI Logistics GmbH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
+          <t>https://www.indeed.com/viewjob?jk=6afcd0c46d1aac2f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Polars, PostgreSQL, MongoDB, ETL, Power BI, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
+          <t>https://www.indeed.com/viewjob?jk=e146f6b8fe54d046</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
+          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
+          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Engineer - Customer Experience</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
+          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
+          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Machine Learning Platform</t>
+          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=a35dc5b0dda48351</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,94 +3051,94 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
+          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Florham Park, NJ, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
+          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
+          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
+          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Digital Analytics Engineer - Customer Experience</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>MLOps Engineer - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
+          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c56248b7666452f</t>
+          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Java QA Automation Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd189429512e52f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a07e922d166cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cellular Sales, Verizon Authorized Retailer</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
+          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Scientist III- Human Capital Data and Analytics Enablement</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Snowflake, NoSQL, Tableau, Git, Python</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6941160617103aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Impact.Com</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Google Cloud Platform, Kafka, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c57f26611e26283</t>
+          <t>https://www.indeed.com/viewjob?jk=8c56248b7666452f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Java QA Automation Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd189429512e52f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IT Business Analyst II</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,17 +3811,367 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03a07e922d166cc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Cellular Sales, Verizon Authorized Retailer</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>L&amp;T Technology Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Novi, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Software Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, NoSQL, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a349add3612b491c</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Software Engineer - Document Generation</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9c88ef97204165d</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Impact.Com</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Engineer - Core Platform</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Unacast</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>IT Business Analyst II</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NFI Industries</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b12be44615688132</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>IDEXX Laboratories</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, SQS, ECS, RDS, Google Cloud Platform, Kafka, NoSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c57f26611e26283</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-27.xlsx
+++ b/results/job_matches_2026-04-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Golang Engineer (AWS | Python | React/Angular/Vue)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8c7a7f43e72aac</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1b4cd21f275b79</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Architect - Job ID 831</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1b4cd21f275b79</t>
+          <t>https://www.indeed.com/viewjob?jk=30116c3087096b0c</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Lakehouse Architect</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SEACORP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Manassas, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Hadoop, Hive, Spark, Scala, Kafka, MongoDB</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677bf2a9ae41af7d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2967a40f711a6e</t>
         </is>
       </c>
     </row>
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2967a40f711a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcce665f3a3b0fee</t>
+          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IAM Compliance</t>
+          <t>Senior Software Engineer - Python APIs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8befff8bb32799</t>
+          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Software engineering intern | Skillsync</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3cac0f27d3d0ec0</t>
+          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0719fad36e544cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DATA SOLUTION ARCHITECT</t>
+          <t>Senior Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Care.org</t>
+          <t>MAERSK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,112 +1046,112 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2846f65aa9294d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Senior Business Intelligence Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Enova International</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42ffff2f95ecf4</t>
+          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Hybrid)</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83247939112593c0</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f063f9c882ccc12</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python APIs</t>
+          <t>SF Technology - Software Engineering - Senior Associate</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00e6d7208f216f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba575b133b119eb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software engineering intern | Skillsync</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a08773ca0782277</t>
+          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer (Hybrid)</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Enova International</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,102 +1266,102 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f180f27ff7393ac</t>
+          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Spark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ee6455a8ca514</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7b3e2ef98acf25</t>
+          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292c1ae20b051cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Senior Cloud Governance Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936f1055bc6513a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Backend Engineer - Integrations</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4f4cd3ad0ce6f5</t>
+          <t>https://www.indeed.com/viewjob?jk=22b8eb7f870c0ec5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06821a24e8c6950</t>
+          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Spark, Scala, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f536b07e93637686</t>
+          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Governance Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Easterseals Southern California</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d20905b5e2faaa0</t>
+          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,15 +1563,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00dd6bd18f4d068</t>
+          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429c2128943540c2</t>
+          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Consultant, AI &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Easterseals Southern California</t>
+          <t>Castleton Tower</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2241b1872054f42d</t>
+          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be902deb0c0cff60</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcb224d87d1611</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Technical Architect - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>WinWire</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, ETL, Jenkins, Docker, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc74bb7856780dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Consultant, AI &amp; Data Engineering</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Castleton Tower</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106bb3c12b0ce283</t>
+          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2084228c36d871bf</t>
+          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Architect</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa3dd413db07a1e</t>
+          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HAVI</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6868b35e2b442275</t>
+          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Technical Architect - Data &amp; Analytics</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668b3d9240bad8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Founding Engineers</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Career Mentors</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37db4c0b07afe64d</t>
+          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=004a99e42e1b83ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cbf54fc5208e3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3753908732fe77ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30f253b6a8acf18</t>
+          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Founding Engineers</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Career Mentors</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, Spark, Kafka, Snowflake, PostgreSQL, dbt, Tableau, MLflow</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20194c0f45aa2c81</t>
+          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35070e714f42f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a751a18a865523</t>
+          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b72f3e295f2b38</t>
+          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Solutions Architect | AI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Trace3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00328cd20addd95f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1563bdd8162e56a</t>
+          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba922bb2fd28863</t>
+          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dae082eb8598575</t>
+          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63486d61003e0a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=daf356dec855c3b1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Solutions Architect | AI</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Trace3</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4d0f879560eea6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d533f19b4463da</t>
+          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa65c57599624378</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,24 +2516,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9230bee4c19c2afb</t>
+          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Google Cloud Platform, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d3c4afd567d4dc</t>
+          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e048a1fa8803abd</t>
+          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Implementation Consultant - Solutions Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dc903c92ca8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2004304d091ff39</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Senior Full Stack Software Development Engineer - AI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, SQS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7d02622748f5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=932a6480f7acd72e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Customer Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reltio</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, DynamoDB, Cassandra, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e739271640a7a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ceebc871c7b716e1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Customer Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HAVI Logistics GmbH</t>
+          <t>Reltio</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, DynamoDB, Cassandra, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6afcd0c46d1aac2f</t>
+          <t>https://www.indeed.com/viewjob?jk=b48f55b509420cd6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Infrastructure Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Polars, PostgreSQL, MongoDB, ETL, Power BI, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e146f6b8fe54d046</t>
+          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d795a30569c6d07</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89664cddc02e354c</t>
+          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f550253b36df98</t>
+          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineering (Palantir, Spark, PySpark, Python)- W2 Role</t>
+          <t>AI/ML Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Numa Management Associates</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, MLOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb73ede58520cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3b8199552143ed2c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2967,11 +2967,11 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35dc5b0dda48351</t>
+          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML Engineering Focus - Remote</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b996573f5f8fa39</t>
+          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff9fd964893cca2</t>
+          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0834fa2eafaef3</t>
+          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aa6a7b0ccb9c57</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Digital Analytics Engineer - Customer Experience</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd06c562a0dd4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>MLOps Engineer - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7837b5aefbcb5351</t>
+          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edebdec5daaa4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Service Cloud Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, PySpark, Scala, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c836f48c3d814cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1335920bcdcf1c</t>
+          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Engineer - Customer Experience</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Scala, Snowflake, Power BI, Tableau, Git, SQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724311be6474c008</t>
+          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Machine Learning Platform</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, GCP, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ff9b97d0d69a97</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Databricks, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b0604cffe8cf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Service Cloud Developer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f7aec210bdd6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Analytics and AI Senior Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377a8106189cff56</t>
+          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Florham Park, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab24ee357dc36621</t>
+          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeab9493cf52705</t>
+          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Braintree, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5fb31b5a0e0aed</t>
+          <t>https://www.indeed.com/viewjob?jk=16ea6e485299a08c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35945946ef347401</t>
+          <t>https://www.indeed.com/viewjob?jk=7b999917838878a9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Azure, Scala, Data Modeling, ELT, MLOps, MLflow, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98baf5e0e0e210ab</t>
+          <t>https://www.indeed.com/viewjob?jk=d71435c6a86e8b64</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ef2ef0698f1fd</t>
+          <t>https://www.indeed.com/viewjob?jk=dc670920196ab795</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Analytics and AI Senior Consultant</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,24 +3706,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16af3b0c4f8842cc</t>
+          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c56248b7666452f</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Java QA Automation Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd189429512e52f</t>
+          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Software Engineer - Core Platform</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Unacast</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a07e922d166cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>IT Business Analyst II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cellular Sales, Verizon Authorized Retailer</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
+          <t>https://www.indeed.com/viewjob?jk=b12be44615688132</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Impact.Com</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aca26123e673da7</t>
+          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Sr. Data Scientist, Programmatic Algorithms</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Impact.Com</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf8975ebf0eb43f</t>
+          <t>https://www.indeed.com/viewjob?jk=0db61ba5b16e71bf</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Cellular Sales, Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Spark, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,217 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bace0705a89432</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Software Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>RDS, NoSQL, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a349add3612b491c</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Software Engineer - Document Generation</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c88ef97204165d</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist, Programmatic Algorithms</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Impact.Com</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, MLOps</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e86578384aa4b6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Software Engineer - Core Platform</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Unacast</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, MySQL, DynamoDB, NoSQL, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=868f8c4ef1ebde56</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>IT Business Analyst II</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>NFI Industries</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Camden, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b12be44615688132</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>IDEXX Laboratories</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Portland, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, SQS, ECS, RDS, Google Cloud Platform, Kafka, NoSQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c57f26611e26283</t>
+          <t>https://www.indeed.com/viewjob?jk=f9313901bc5ac9da</t>
         </is>
       </c>
     </row>
